--- a/salidas/empresas/PM.xlsx
+++ b/salidas/empresas/PM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B2" t="n">
-        <v>21.65662384033203</v>
+        <v>21.6566276550293</v>
       </c>
       <c r="C2" t="n">
         <v>50.58000183105469</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B3" t="n">
-        <v>21.84928894042969</v>
+        <v>21.84929275512695</v>
       </c>
       <c r="C3" t="n">
         <v>51.02999877929688</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B4" t="n">
-        <v>22.54720878601074</v>
+        <v>22.54720115661621</v>
       </c>
       <c r="C4" t="n">
         <v>52.65999984741211</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B5" t="n">
-        <v>21.33668899536133</v>
+        <v>21.33669090270996</v>
       </c>
       <c r="C5" t="n">
         <v>49.38999938964844</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B6" t="n">
-        <v>22.31301307678223</v>
+        <v>22.31302070617676</v>
       </c>
       <c r="C6" t="n">
         <v>51.65000152587891</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B7" t="n">
-        <v>23.19863319396973</v>
+        <v>23.19862365722656</v>
       </c>
       <c r="C7" t="n">
         <v>53.70000076293945</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B8" t="n">
-        <v>20.98688507080078</v>
+        <v>20.98689079284668</v>
       </c>
       <c r="C8" t="n">
         <v>48.09999847412109</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B9" t="n">
-        <v>18.96673965454102</v>
+        <v>18.96674156188965</v>
       </c>
       <c r="C9" t="n">
         <v>43.47000122070312</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B10" t="n">
-        <v>18.39516258239746</v>
+        <v>18.39516067504883</v>
       </c>
       <c r="C10" t="n">
         <v>42.15999984741211</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B11" t="n">
-        <v>19.23044776916504</v>
+        <v>19.23044395446777</v>
       </c>
       <c r="C11" t="n">
         <v>43.5099983215332</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B12" t="n">
-        <v>16.41946411132812</v>
+        <v>16.41947174072266</v>
       </c>
       <c r="C12" t="n">
         <v>37.15000152587891</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B13" t="n">
-        <v>14.79299163818359</v>
+        <v>14.79299068450928</v>
       </c>
       <c r="C13" t="n">
         <v>33.47000122070312</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B14" t="n">
-        <v>15.95009326934814</v>
+        <v>15.95009994506836</v>
       </c>
       <c r="C14" t="n">
         <v>35.58000183105469</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B15" t="n">
-        <v>16.22803688049316</v>
+        <v>16.22804069519043</v>
       </c>
       <c r="C15" t="n">
         <v>36.20000076293945</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B16" t="n">
-        <v>19.11500549316406</v>
+        <v>19.11501312255859</v>
       </c>
       <c r="C16" t="n">
         <v>42.63999938964844</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B17" t="n">
-        <v>19.80809593200684</v>
+        <v>19.80810546875</v>
       </c>
       <c r="C17" t="n">
         <v>43.61999893188477</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B18" t="n">
-        <v>21.16133880615234</v>
+        <v>21.16134262084961</v>
       </c>
       <c r="C18" t="n">
         <v>46.59999847412109</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B19" t="n">
-        <v>20.75718116760254</v>
+        <v>20.75718307495117</v>
       </c>
       <c r="C19" t="n">
         <v>45.70999908447266</v>
@@ -830,7 +842,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B20" t="n">
@@ -855,11 +867,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B21" t="n">
-        <v>21.76195907592773</v>
+        <v>21.761962890625</v>
       </c>
       <c r="C21" t="n">
         <v>47.36000061035156</v>
@@ -880,11 +892,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B22" t="n">
-        <v>22.09739875793457</v>
+        <v>22.09739685058594</v>
       </c>
       <c r="C22" t="n">
         <v>48.09000015258789</v>
@@ -905,11 +917,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B23" t="n">
-        <v>22.40533828735352</v>
+        <v>22.40534591674805</v>
       </c>
       <c r="C23" t="n">
         <v>48.18999862670898</v>
@@ -930,11 +942,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B24" t="n">
-        <v>21.1593074798584</v>
+        <v>21.15930938720703</v>
       </c>
       <c r="C24" t="n">
         <v>45.5099983215332</v>
@@ -955,7 +967,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B25" t="n">
@@ -980,11 +992,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B26" t="n">
-        <v>24.52003288269043</v>
+        <v>24.52004051208496</v>
       </c>
       <c r="C26" t="n">
         <v>52.15999984741211</v>
@@ -1005,11 +1017,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B27" t="n">
-        <v>23.0721549987793</v>
+        <v>23.07215309143066</v>
       </c>
       <c r="C27" t="n">
         <v>49.08000183105469</v>
@@ -1030,11 +1042,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B28" t="n">
-        <v>20.74048805236816</v>
+        <v>20.74049186706543</v>
       </c>
       <c r="C28" t="n">
         <v>44.11999893188477</v>
@@ -1055,11 +1067,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B29" t="n">
-        <v>21.82248497009277</v>
+        <v>21.82248687744141</v>
       </c>
       <c r="C29" t="n">
         <v>45.84000015258789</v>
@@ -1080,7 +1092,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B30" t="n">
@@ -1105,7 +1117,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B31" t="n">
@@ -1130,7 +1142,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B32" t="n">
@@ -1155,11 +1167,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B33" t="n">
-        <v>28.17589950561523</v>
+        <v>28.17591857910156</v>
       </c>
       <c r="C33" t="n">
         <v>58.5099983215332</v>
@@ -1180,11 +1192,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B34" t="n">
-        <v>27.39579391479492</v>
+        <v>27.39579010009766</v>
       </c>
       <c r="C34" t="n">
         <v>56.88999938964844</v>
@@ -1205,11 +1217,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B35" t="n">
-        <v>28.49164581298828</v>
+        <v>28.49164390563965</v>
       </c>
       <c r="C35" t="n">
         <v>58.52999877929688</v>
@@ -1230,11 +1242,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B36" t="n">
-        <v>27.86369895935059</v>
+        <v>27.86367988586426</v>
       </c>
       <c r="C36" t="n">
         <v>57.2400016784668</v>
@@ -1255,11 +1267,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B37" t="n">
-        <v>30.56049537658691</v>
+        <v>30.56049156188965</v>
       </c>
       <c r="C37" t="n">
         <v>62.77999877929688</v>
@@ -1284,11 +1296,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B38" t="n">
-        <v>32.2759895324707</v>
+        <v>32.27597427368164</v>
       </c>
       <c r="C38" t="n">
         <v>65.62999725341797</v>
@@ -1313,11 +1325,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B39" t="n">
-        <v>34.14969635009766</v>
+        <v>34.14969253540039</v>
       </c>
       <c r="C39" t="n">
         <v>69.44000244140625</v>
@@ -1342,11 +1354,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B40" t="n">
-        <v>35.28573608398438</v>
+        <v>35.28572463989258</v>
       </c>
       <c r="C40" t="n">
         <v>71.75</v>
@@ -1371,11 +1383,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B41" t="n">
-        <v>33.1436767578125</v>
+        <v>33.14368438720703</v>
       </c>
       <c r="C41" t="n">
         <v>66.76999664306641</v>
@@ -1400,11 +1412,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B42" t="n">
-        <v>35.32778549194336</v>
+        <v>35.32776260375977</v>
       </c>
       <c r="C42" t="n">
         <v>71.16999816894531</v>
@@ -1429,11 +1441,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B43" t="n">
-        <v>34.40946578979492</v>
+        <v>34.40947341918945</v>
       </c>
       <c r="C43" t="n">
         <v>69.31999969482422</v>
@@ -1458,11 +1470,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B44" t="n">
-        <v>31.33597946166992</v>
+        <v>31.33598518371582</v>
       </c>
       <c r="C44" t="n">
         <v>62.38000106811523</v>
@@ -1487,11 +1499,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B45" t="n">
-        <v>35.0985221862793</v>
+        <v>35.0985107421875</v>
       </c>
       <c r="C45" t="n">
         <v>69.87000274658203</v>
@@ -1516,11 +1528,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B46" t="n">
-        <v>38.29844284057617</v>
+        <v>38.29842376708984</v>
       </c>
       <c r="C46" t="n">
         <v>76.23999786376953</v>
@@ -1545,11 +1557,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B47" t="n">
-        <v>39.82611846923828</v>
+        <v>39.82609939575195</v>
       </c>
       <c r="C47" t="n">
         <v>78.48000335693359</v>
@@ -1574,7 +1586,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B48" t="n">
@@ -1603,11 +1615,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B49" t="n">
-        <v>42.38375473022461</v>
+        <v>42.38376235961914</v>
       </c>
       <c r="C49" t="n">
         <v>83.51999664306641</v>
@@ -1632,11 +1644,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B50" t="n">
-        <v>45.36301803588867</v>
+        <v>45.36301422119141</v>
       </c>
       <c r="C50" t="n">
         <v>88.61000061035156</v>
@@ -1661,11 +1673,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B51" t="n">
-        <v>45.82376480102539</v>
+        <v>45.82376861572266</v>
       </c>
       <c r="C51" t="n">
         <v>89.51000213623047</v>
@@ -1690,11 +1702,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B52" t="n">
-        <v>43.26406478881836</v>
+        <v>43.26407241821289</v>
       </c>
       <c r="C52" t="n">
         <v>84.51000213623047</v>
@@ -1719,11 +1731,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B53" t="n">
-        <v>45.07543182373047</v>
+        <v>45.07544326782227</v>
       </c>
       <c r="C53" t="n">
         <v>87.26000213623047</v>
@@ -1748,11 +1760,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B54" t="n">
-        <v>47.23469161987305</v>
+        <v>47.23468017578125</v>
       </c>
       <c r="C54" t="n">
         <v>91.44000244140625</v>
@@ -1777,11 +1789,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B55" t="n">
-        <v>46.12922668457031</v>
+        <v>46.12922286987305</v>
       </c>
       <c r="C55" t="n">
         <v>89.30000305175781</v>
@@ -1806,11 +1818,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B56" t="n">
-        <v>46.89245986938477</v>
+        <v>46.8924560546875</v>
       </c>
       <c r="C56" t="n">
         <v>89.94000244140625</v>
@@ -1835,11 +1847,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B57" t="n">
-        <v>46.17296981811523</v>
+        <v>46.1729621887207</v>
       </c>
       <c r="C57" t="n">
         <v>88.55999755859375</v>
@@ -1864,11 +1876,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B58" t="n">
-        <v>46.86116409301758</v>
+        <v>46.86116790771484</v>
       </c>
       <c r="C58" t="n">
         <v>89.87999725341797</v>
@@ -1893,11 +1905,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B59" t="n">
-        <v>43.67159652709961</v>
+        <v>43.67158889770508</v>
       </c>
       <c r="C59" t="n">
         <v>83.63999938964844</v>
@@ -1922,11 +1934,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B60" t="n">
-        <v>46.03166198730469</v>
+        <v>46.03166961669922</v>
       </c>
       <c r="C60" t="n">
         <v>88.16000366210938</v>
@@ -1951,11 +1963,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B61" t="n">
-        <v>47.90615081787109</v>
+        <v>47.90613555908203</v>
       </c>
       <c r="C61" t="n">
         <v>91.75</v>
@@ -1980,7 +1992,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B62" t="n">
@@ -2009,11 +2021,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B63" t="n">
-        <v>50.37662887573242</v>
+        <v>50.37662506103516</v>
       </c>
       <c r="C63" t="n">
         <v>95.58999633789062</v>
@@ -2038,7 +2050,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B64" t="n">
@@ -2067,11 +2079,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B65" t="n">
-        <v>46.10055923461914</v>
+        <v>46.10057830810547</v>
       </c>
       <c r="C65" t="n">
         <v>86.62000274658203</v>
@@ -2096,11 +2108,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B66" t="n">
-        <v>47.46302032470703</v>
+        <v>47.46303939819336</v>
       </c>
       <c r="C66" t="n">
         <v>89.18000030517578</v>
@@ -2125,11 +2137,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B67" t="n">
-        <v>44.40811920166016</v>
+        <v>44.40808868408203</v>
       </c>
       <c r="C67" t="n">
         <v>83.44000244140625</v>
@@ -2154,11 +2166,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B68" t="n">
-        <v>46.57238006591797</v>
+        <v>46.57234954833984</v>
       </c>
       <c r="C68" t="n">
         <v>86.58999633789062</v>
@@ -2183,7 +2195,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B69" t="n">
@@ -2212,11 +2224,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B70" t="n">
-        <v>46.00762557983398</v>
+        <v>46.00763320922852</v>
       </c>
       <c r="C70" t="n">
         <v>85.54000091552734</v>
@@ -2241,11 +2253,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B71" t="n">
-        <v>47.38364028930664</v>
+        <v>47.38363265991211</v>
       </c>
       <c r="C71" t="n">
         <v>87.12999725341797</v>
@@ -2270,11 +2282,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B72" t="n">
-        <v>42.49463272094727</v>
+        <v>42.49462127685547</v>
       </c>
       <c r="C72" t="n">
         <v>78.13999938964844</v>
@@ -2299,11 +2311,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B73" t="n">
-        <v>44.00104141235352</v>
+        <v>44.00103378295898</v>
       </c>
       <c r="C73" t="n">
         <v>80.91000366210938</v>
@@ -2328,11 +2340,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B74" t="n">
-        <v>45.04966354370117</v>
+        <v>45.0496711730957</v>
       </c>
       <c r="C74" t="n">
         <v>81.87000274658203</v>
@@ -2357,11 +2369,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B75" t="n">
-        <v>47.00859451293945</v>
+        <v>47.00859069824219</v>
       </c>
       <c r="C75" t="n">
         <v>85.43000030517578</v>
@@ -2386,11 +2398,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B76" t="n">
-        <v>48.71989440917969</v>
+        <v>48.71990203857422</v>
       </c>
       <c r="C76" t="n">
         <v>88.54000091552734</v>
@@ -2415,11 +2427,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B77" t="n">
-        <v>46.87961196899414</v>
+        <v>46.87960433959961</v>
       </c>
       <c r="C77" t="n">
         <v>84.30999755859375</v>
@@ -2444,11 +2456,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B78" t="n">
-        <v>45.60072326660156</v>
+        <v>45.60071563720703</v>
       </c>
       <c r="C78" t="n">
         <v>82.01000213623047</v>
@@ -2473,11 +2485,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B79" t="n">
-        <v>47.58576583862305</v>
+        <v>47.58576965332031</v>
       </c>
       <c r="C79" t="n">
         <v>85.58000183105469</v>
@@ -2502,11 +2514,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B80" t="n">
-        <v>46.91884994506836</v>
+        <v>46.91887283325195</v>
       </c>
       <c r="C80" t="n">
         <v>83.40000152587891</v>
@@ -2531,7 +2543,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B81" t="n">
@@ -2560,11 +2572,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B82" t="n">
-        <v>48.90475845336914</v>
+        <v>48.90476226806641</v>
       </c>
       <c r="C82" t="n">
         <v>86.93000030517578</v>
@@ -2589,11 +2601,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B83" t="n">
-        <v>46.38029861450195</v>
+        <v>46.38030242919922</v>
       </c>
       <c r="C83" t="n">
         <v>81.44999694824219</v>
@@ -2618,11 +2630,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B84" t="n">
-        <v>45.6912956237793</v>
+        <v>45.6912841796875</v>
       </c>
       <c r="C84" t="n">
         <v>80.23999786376953</v>
@@ -2647,11 +2659,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B85" t="n">
-        <v>47.24013519287109</v>
+        <v>47.24014663696289</v>
       </c>
       <c r="C85" t="n">
         <v>82.95999908447266</v>
@@ -2676,11 +2688,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B86" t="n">
-        <v>43.43931198120117</v>
+        <v>43.43931579589844</v>
       </c>
       <c r="C86" t="n">
         <v>75.33000183105469</v>
@@ -2705,11 +2717,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B87" t="n">
-        <v>48.13326263427734</v>
+        <v>48.13327789306641</v>
       </c>
       <c r="C87" t="n">
         <v>83.47000122070312</v>
@@ -2734,7 +2746,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B88" t="n">
@@ -2763,11 +2775,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B89" t="n">
-        <v>46.79320907592773</v>
+        <v>46.79320526123047</v>
       </c>
       <c r="C89" t="n">
         <v>80.16999816894531</v>
@@ -2792,11 +2804,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B90" t="n">
-        <v>49.92169952392578</v>
+        <v>49.92171478271484</v>
       </c>
       <c r="C90" t="n">
         <v>85.52999877929688</v>
@@ -2821,11 +2833,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B91" t="n">
-        <v>46.57725524902344</v>
+        <v>46.57724761962891</v>
       </c>
       <c r="C91" t="n">
         <v>79.80000305175781</v>
@@ -2850,11 +2862,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B92" t="n">
-        <v>46.89640045166016</v>
+        <v>46.89640808105469</v>
       </c>
       <c r="C92" t="n">
         <v>79.33000183105469</v>
@@ -2879,11 +2891,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B93" t="n">
-        <v>52.25818252563477</v>
+        <v>52.2581787109375</v>
       </c>
       <c r="C93" t="n">
         <v>88.40000152587891</v>
@@ -2908,11 +2920,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B94" t="n">
-        <v>51.66111373901367</v>
+        <v>51.6611213684082</v>
       </c>
       <c r="C94" t="n">
         <v>87.38999938964844</v>
@@ -2937,11 +2949,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B95" t="n">
-        <v>52.58559799194336</v>
+        <v>52.58562088012695</v>
       </c>
       <c r="C95" t="n">
         <v>87.91000366210938</v>
@@ -2966,11 +2978,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B96" t="n">
-        <v>53.84177017211914</v>
+        <v>53.84177398681641</v>
       </c>
       <c r="C96" t="n">
         <v>90.01000213623047</v>
@@ -2995,11 +3007,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B97" t="n">
-        <v>54.45191192626953</v>
+        <v>54.45189666748047</v>
       </c>
       <c r="C97" t="n">
         <v>91.02999877929688</v>
@@ -3024,11 +3036,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B98" t="n">
-        <v>59.30051803588867</v>
+        <v>59.30051422119141</v>
       </c>
       <c r="C98" t="n">
         <v>98.11000061035156</v>
@@ -3053,11 +3065,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B99" t="n">
-        <v>59.30654144287109</v>
+        <v>59.30655288696289</v>
       </c>
       <c r="C99" t="n">
         <v>98.12000274658203</v>
@@ -3082,11 +3094,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B100" t="n">
-        <v>59.64501953125</v>
+        <v>59.64503860473633</v>
       </c>
       <c r="C100" t="n">
         <v>98.68000030517578</v>
@@ -3111,11 +3123,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B101" t="n">
-        <v>62.10631561279297</v>
+        <v>62.1063232421875</v>
       </c>
       <c r="C101" t="n">
         <v>101.7200012207031</v>
@@ -3140,11 +3152,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B102" t="n">
-        <v>61.21490859985352</v>
+        <v>61.21490478515625</v>
       </c>
       <c r="C102" t="n">
         <v>100.2600021362305</v>
@@ -3169,11 +3181,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B103" t="n">
-        <v>61.01340866088867</v>
+        <v>61.013427734375</v>
       </c>
       <c r="C103" t="n">
         <v>99.93000030517578</v>
@@ -3198,11 +3210,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B104" t="n">
-        <v>59.97310256958008</v>
+        <v>59.97312545776367</v>
       </c>
       <c r="C104" t="n">
         <v>97.22000122070312</v>
@@ -3227,11 +3239,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B105" t="n">
-        <v>59.4919319152832</v>
+        <v>59.49194717407227</v>
       </c>
       <c r="C105" t="n">
         <v>96.44000244140625</v>
@@ -3256,11 +3268,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B106" t="n">
-        <v>54.45818710327148</v>
+        <v>54.45820236206055</v>
       </c>
       <c r="C106" t="n">
         <v>88.27999877929688</v>
@@ -3285,11 +3297,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B107" t="n">
-        <v>57.08753967285156</v>
+        <v>57.0875244140625</v>
       </c>
       <c r="C107" t="n">
         <v>91.48999786376953</v>
@@ -3314,11 +3326,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B108" t="n">
-        <v>59.9827880859375</v>
+        <v>59.98278045654297</v>
       </c>
       <c r="C108" t="n">
         <v>96.12999725341797</v>
@@ -3343,11 +3355,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B109" t="n">
-        <v>68.23172760009766</v>
+        <v>68.23174285888672</v>
       </c>
       <c r="C109" t="n">
         <v>109.3499984741211</v>
@@ -3372,7 +3384,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B110" t="n">
@@ -3401,11 +3413,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B111" t="n">
-        <v>69.79815673828125</v>
+        <v>69.79817199707031</v>
       </c>
       <c r="C111" t="n">
         <v>110.8399963378906</v>
@@ -3430,11 +3442,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B112" t="n">
-        <v>75.44044494628906</v>
+        <v>75.44046020507812</v>
       </c>
       <c r="C112" t="n">
         <v>119.8000030517578</v>
@@ -3459,7 +3471,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B113" t="n">
@@ -3488,11 +3500,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B114" t="n">
-        <v>74.12593841552734</v>
+        <v>74.12592315673828</v>
       </c>
       <c r="C114" t="n">
         <v>116.7099990844727</v>
@@ -3517,11 +3529,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B115" t="n">
-        <v>74.26567077636719</v>
+        <v>74.26566314697266</v>
       </c>
       <c r="C115" t="n">
         <v>116.9300003051758</v>
@@ -3546,11 +3558,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B116" t="n">
-        <v>71.17820739746094</v>
+        <v>71.17822265625</v>
       </c>
       <c r="C116" t="n">
         <v>111.0100021362305</v>
@@ -3575,11 +3587,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B117" t="n">
-        <v>67.09383392333984</v>
+        <v>67.09384918212891</v>
       </c>
       <c r="C117" t="n">
         <v>104.6399993896484</v>
@@ -3604,11 +3616,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B118" t="n">
-        <v>65.88200378417969</v>
+        <v>65.88198852539062</v>
       </c>
       <c r="C118" t="n">
         <v>102.75</v>
@@ -3633,11 +3645,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B119" t="n">
-        <v>68.41853332519531</v>
+        <v>68.41855621337891</v>
       </c>
       <c r="C119" t="n">
         <v>105.6500015258789</v>
@@ -3662,11 +3674,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B120" t="n">
-        <v>69.44174194335938</v>
+        <v>69.44172668457031</v>
       </c>
       <c r="C120" t="n">
         <v>107.2300033569336</v>
@@ -3691,11 +3703,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B121" t="n">
-        <v>67.05857086181641</v>
+        <v>67.05859375</v>
       </c>
       <c r="C121" t="n">
         <v>103.5500030517578</v>
@@ -3720,11 +3732,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B122" t="n">
-        <v>65.06539154052734</v>
+        <v>65.06538391113281</v>
       </c>
       <c r="C122" t="n">
         <v>99.40000152587891</v>
@@ -3749,11 +3761,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B123" t="n">
-        <v>53.6756706237793</v>
+        <v>53.67568206787109</v>
       </c>
       <c r="C123" t="n">
         <v>82</v>
@@ -3778,11 +3790,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B124" t="n">
-        <v>52.06540298461914</v>
+        <v>52.06540679931641</v>
       </c>
       <c r="C124" t="n">
         <v>79.54000091552734</v>
@@ -3807,11 +3819,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B125" t="n">
-        <v>53.59831237792969</v>
+        <v>53.59832382202148</v>
       </c>
       <c r="C125" t="n">
         <v>80.73999786376953</v>
@@ -3836,11 +3848,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B126" t="n">
-        <v>57.28928756713867</v>
+        <v>57.28925704956055</v>
       </c>
       <c r="C126" t="n">
         <v>86.30000305175781</v>
@@ -3865,11 +3877,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B127" t="n">
-        <v>51.70639419555664</v>
+        <v>51.70638275146484</v>
       </c>
       <c r="C127" t="n">
         <v>77.88999938964844</v>
@@ -3894,11 +3906,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B128" t="n">
-        <v>54.89624786376953</v>
+        <v>54.896240234375</v>
       </c>
       <c r="C128" t="n">
         <v>81.54000091552734</v>
@@ -3923,11 +3935,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B129" t="n">
-        <v>59.29251098632812</v>
+        <v>59.29250717163086</v>
       </c>
       <c r="C129" t="n">
         <v>88.06999969482422</v>
@@ -3952,11 +3964,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B130" t="n">
-        <v>58.25572967529297</v>
+        <v>58.2557373046875</v>
       </c>
       <c r="C130" t="n">
         <v>86.52999877929688</v>
@@ -3981,11 +3993,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B131" t="n">
-        <v>45.63783645629883</v>
+        <v>45.63784027099609</v>
       </c>
       <c r="C131" t="n">
         <v>66.76000213623047</v>
@@ -4010,11 +4022,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B132" t="n">
-        <v>52.44659042358398</v>
+        <v>52.44659805297852</v>
       </c>
       <c r="C132" t="n">
         <v>76.72000122070312</v>
@@ -4039,11 +4051,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B133" t="n">
-        <v>59.43309783935547</v>
+        <v>59.43308258056641</v>
       </c>
       <c r="C133" t="n">
         <v>86.94000244140625</v>
@@ -4068,7 +4080,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B134" t="n">
@@ -4097,11 +4109,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B135" t="n">
-        <v>59.92261505126953</v>
+        <v>59.92258834838867</v>
       </c>
       <c r="C135" t="n">
         <v>86.55999755859375</v>
@@ -4126,7 +4138,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B136" t="n">
@@ -4155,11 +4167,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B137" t="n">
-        <v>55.18444442749023</v>
+        <v>55.1844482421875</v>
       </c>
       <c r="C137" t="n">
         <v>78.52999877929688</v>
@@ -4184,7 +4196,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B138" t="n">
@@ -4213,11 +4225,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B139" t="n">
-        <v>50.65893173217773</v>
+        <v>50.65893936157227</v>
       </c>
       <c r="C139" t="n">
         <v>72.08999633789062</v>
@@ -4242,11 +4254,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B140" t="n">
-        <v>54.23875427246094</v>
+        <v>54.2387580871582</v>
       </c>
       <c r="C140" t="n">
         <v>75.93000030517578</v>
@@ -4271,11 +4283,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B141" t="n">
-        <v>58.17467880249023</v>
+        <v>58.17471694946289</v>
       </c>
       <c r="C141" t="n">
         <v>81.44000244140625</v>
@@ -4300,11 +4312,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B142" t="n">
-        <v>59.23904037475586</v>
+        <v>59.23903274536133</v>
       </c>
       <c r="C142" t="n">
         <v>82.93000030517578</v>
@@ -4329,7 +4341,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B143" t="n">
@@ -4358,11 +4370,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B144" t="n">
-        <v>59.88998031616211</v>
+        <v>59.88999176025391</v>
       </c>
       <c r="C144" t="n">
         <v>82.69999694824219</v>
@@ -4387,7 +4399,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B145" t="n">
@@ -4416,11 +4428,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B146" t="n">
-        <v>53.78371810913086</v>
+        <v>53.78371047973633</v>
       </c>
       <c r="C146" t="n">
         <v>72.95999908447266</v>
@@ -4445,11 +4457,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B147" t="n">
-        <v>54.99267959594727</v>
+        <v>54.99267578125</v>
       </c>
       <c r="C147" t="n">
         <v>74.59999847412109</v>
@@ -4474,11 +4486,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B148" t="n">
-        <v>54.07859039306641</v>
+        <v>54.07858657836914</v>
       </c>
       <c r="C148" t="n">
         <v>73.36000061035156</v>
@@ -4503,11 +4515,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B149" t="n">
-        <v>52.46882629394531</v>
+        <v>52.46882247924805</v>
       </c>
       <c r="C149" t="n">
         <v>70.05999755859375</v>
@@ -4532,11 +4544,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B150" t="n">
-        <v>57.52399444580078</v>
+        <v>57.52400207519531</v>
       </c>
       <c r="C150" t="n">
         <v>76.80999755859375</v>
@@ -4561,11 +4573,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B151" t="n">
-        <v>59.75574111938477</v>
+        <v>59.75576782226562</v>
       </c>
       <c r="C151" t="n">
         <v>79.79000091552734</v>
@@ -4590,7 +4602,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B152" t="n">
@@ -4619,11 +4631,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B153" t="n">
-        <v>54.02970123291016</v>
+        <v>54.02969360351562</v>
       </c>
       <c r="C153" t="n">
         <v>71.01999664306641</v>
@@ -4648,11 +4660,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B154" t="n">
-        <v>57.62812423706055</v>
+        <v>57.62813949584961</v>
       </c>
       <c r="C154" t="n">
         <v>75.75</v>
@@ -4677,11 +4689,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B155" t="n">
-        <v>63.89487457275391</v>
+        <v>63.89486694335938</v>
       </c>
       <c r="C155" t="n">
         <v>82.79000091552734</v>
@@ -4706,11 +4718,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B156" t="n">
-        <v>61.47151184082031</v>
+        <v>61.47153854370117</v>
       </c>
       <c r="C156" t="n">
         <v>79.65000152587891</v>
@@ -4735,11 +4747,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B157" t="n">
-        <v>64.84415435791016</v>
+        <v>64.84413909912109</v>
       </c>
       <c r="C157" t="n">
         <v>84.01999664306641</v>
@@ -4764,11 +4776,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B158" t="n">
-        <v>69.40658569335938</v>
+        <v>69.40659332275391</v>
       </c>
       <c r="C158" t="n">
         <v>88.73999786376953</v>
@@ -4793,11 +4805,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B159" t="n">
-        <v>74.30275726318359</v>
+        <v>74.30277252197266</v>
       </c>
       <c r="C159" t="n">
         <v>95</v>
@@ -4822,11 +4834,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B160" t="n">
-        <v>75.42120361328125</v>
+        <v>75.42124176025391</v>
       </c>
       <c r="C160" t="n">
         <v>96.43000030517578</v>
@@ -4851,11 +4863,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B161" t="n">
-        <v>78.4583740234375</v>
+        <v>78.45835876464844</v>
       </c>
       <c r="C161" t="n">
         <v>99.11000061035156</v>
@@ -4880,11 +4892,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B162" t="n">
-        <v>79.23415374755859</v>
+        <v>79.23416137695312</v>
       </c>
       <c r="C162" t="n">
         <v>100.0899963378906</v>
@@ -4909,11 +4921,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B163" t="n">
-        <v>81.53780364990234</v>
+        <v>81.53779602050781</v>
       </c>
       <c r="C163" t="n">
         <v>103</v>
@@ -4938,11 +4950,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B164" t="n">
-        <v>75.96485900878906</v>
+        <v>75.96483612060547</v>
       </c>
       <c r="C164" t="n">
         <v>94.79000091552734</v>
@@ -4967,11 +4979,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B165" t="n">
-        <v>75.76448822021484</v>
+        <v>75.76448059082031</v>
       </c>
       <c r="C165" t="n">
         <v>94.54000091552734</v>
@@ -4996,11 +5008,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B166" t="n">
-        <v>68.87242889404297</v>
+        <v>68.87244415283203</v>
       </c>
       <c r="C166" t="n">
         <v>85.94000244140625</v>
@@ -5025,11 +5037,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B167" t="n">
-        <v>77.169921875</v>
+        <v>77.16992950439453</v>
       </c>
       <c r="C167" t="n">
         <v>95</v>
@@ -5054,7 +5066,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B168" t="n">
@@ -5083,11 +5095,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B169" t="n">
-        <v>82.10066986083984</v>
+        <v>82.10067749023438</v>
       </c>
       <c r="C169" t="n">
         <v>101.0699996948242</v>
@@ -5112,11 +5124,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B170" t="n">
-        <v>77.3411865234375</v>
+        <v>77.34117889404297</v>
       </c>
       <c r="C170" t="n">
         <v>93.94000244140625</v>
@@ -5141,11 +5153,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B171" t="n">
-        <v>82.33038330078125</v>
+        <v>82.33040618896484</v>
       </c>
       <c r="C171" t="n">
         <v>100</v>
@@ -5170,11 +5182,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B172" t="n">
-        <v>87.47605133056641</v>
+        <v>87.47604370117188</v>
       </c>
       <c r="C172" t="n">
         <v>106.25</v>
@@ -5199,11 +5211,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B173" t="n">
-        <v>82.31307983398438</v>
+        <v>82.31307220458984</v>
       </c>
       <c r="C173" t="n">
         <v>98.73999786376953</v>
@@ -5228,11 +5240,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B174" t="n">
-        <v>80.98758697509766</v>
+        <v>80.98760223388672</v>
       </c>
       <c r="C174" t="n">
         <v>97.15000152587891</v>
@@ -5257,11 +5269,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B175" t="n">
-        <v>79.603759765625</v>
+        <v>79.60376739501953</v>
       </c>
       <c r="C175" t="n">
         <v>95.48999786376953</v>
@@ -5286,7 +5298,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B176" t="n">
@@ -5315,11 +5327,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B177" t="n">
-        <v>77.66317749023438</v>
+        <v>77.66318511962891</v>
       </c>
       <c r="C177" t="n">
         <v>91.84999847412109</v>
@@ -5344,11 +5356,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B178" t="n">
-        <v>84.27532196044922</v>
+        <v>84.27533721923828</v>
       </c>
       <c r="C178" t="n">
         <v>99.66999816894531</v>
@@ -5373,11 +5385,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B179" t="n">
-        <v>86.66810607910156</v>
+        <v>86.66811370849609</v>
       </c>
       <c r="C179" t="n">
         <v>101.2099990844727</v>
@@ -5402,11 +5414,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B180" t="n">
-        <v>89.26277160644531</v>
+        <v>89.26275634765625</v>
       </c>
       <c r="C180" t="n">
         <v>104.2399978637695</v>
@@ -5431,7 +5443,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B181" t="n">
@@ -5460,7 +5472,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B182" t="n">
@@ -5489,11 +5501,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B183" t="n">
-        <v>86.75760650634766</v>
+        <v>86.75762176513672</v>
       </c>
       <c r="C183" t="n">
         <v>99.97000122070312</v>
@@ -5518,7 +5530,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B184" t="n">
@@ -5547,7 +5559,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B185" t="n">
@@ -5576,11 +5588,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B186" t="n">
-        <v>87.69658660888672</v>
+        <v>87.69657897949219</v>
       </c>
       <c r="C186" t="n">
         <v>99.72000122070312</v>
@@ -5605,11 +5617,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B187" t="n">
-        <v>84.47787475585938</v>
+        <v>84.47785949707031</v>
       </c>
       <c r="C187" t="n">
         <v>96.05999755859375</v>
@@ -5634,11 +5646,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B188" t="n">
-        <v>82.56271362304688</v>
+        <v>82.56270599365234</v>
       </c>
       <c r="C188" t="n">
         <v>92.58000183105469</v>
@@ -5663,7 +5675,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B189" t="n">
@@ -5692,7 +5704,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B190" t="n">
@@ -5721,11 +5733,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B191" t="n">
-        <v>85.06110382080078</v>
+        <v>85.06109619140625</v>
       </c>
       <c r="C191" t="n">
         <v>94.08000183105469</v>
@@ -5750,7 +5762,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B192" t="n">
@@ -5779,11 +5791,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B193" t="n">
-        <v>81.3360595703125</v>
+        <v>81.33606719970703</v>
       </c>
       <c r="C193" t="n">
         <v>89.95999908447266</v>
@@ -5808,11 +5820,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B194" t="n">
-        <v>83.98644256591797</v>
+        <v>83.98645782470703</v>
       </c>
       <c r="C194" t="n">
         <v>91.62000274658203</v>
@@ -5837,11 +5849,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B195" t="n">
-        <v>87.02983093261719</v>
+        <v>87.02983856201172</v>
       </c>
       <c r="C195" t="n">
         <v>94.94000244140625</v>
@@ -5866,11 +5878,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
-        <v>92.93327331542969</v>
+        <v>92.93326568603516</v>
       </c>
       <c r="C196" t="n">
         <v>101.379997253418</v>
@@ -5895,11 +5907,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B197" t="n">
-        <v>94.09619903564453</v>
+        <v>94.09619140625</v>
       </c>
       <c r="C197" t="n">
         <v>101.3300018310547</v>
@@ -5924,11 +5936,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B198" t="n">
-        <v>106.9388961791992</v>
+        <v>106.9388885498047</v>
       </c>
       <c r="C198" t="n">
         <v>115.1600036621094</v>
@@ -5953,11 +5965,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B199" t="n">
-        <v>114.4885025024414</v>
+        <v>114.4884948730469</v>
       </c>
       <c r="C199" t="n">
         <v>123.2900009155273</v>
@@ -5982,7 +5994,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B200" t="n">
@@ -6011,11 +6023,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B201" t="n">
-        <v>124.6090927124023</v>
+        <v>124.6091003417969</v>
       </c>
       <c r="C201" t="n">
         <v>132.6999969482422</v>
@@ -6040,11 +6052,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B202" t="n">
-        <v>124.9471588134766</v>
+        <v>124.947135925293</v>
       </c>
       <c r="C202" t="n">
         <v>133.0599975585938</v>
@@ -6069,11 +6081,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B203" t="n">
-        <v>114.2671661376953</v>
+        <v>114.2671737670898</v>
       </c>
       <c r="C203" t="n">
         <v>120.3499984741211</v>
@@ -6098,11 +6110,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B204" t="n">
-        <v>123.6193237304688</v>
+        <v>123.6193313598633</v>
       </c>
       <c r="C204" t="n">
         <v>130.1999969482422</v>
@@ -6127,7 +6139,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B205" t="n">
@@ -6156,7 +6168,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B206" t="n">
@@ -6185,11 +6197,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B207" t="n">
-        <v>164.1351165771484</v>
+        <v>164.1351318359375</v>
       </c>
       <c r="C207" t="n">
         <v>171.3600006103516</v>
@@ -6214,11 +6226,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B208" t="n">
-        <v>172.9759674072266</v>
+        <v>172.9759826660156</v>
       </c>
       <c r="C208" t="n">
         <v>180.5899963378906</v>
@@ -6243,7 +6255,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B209" t="n">
@@ -6272,11 +6284,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B210" t="n">
-        <v>158.3163757324219</v>
+        <v>158.3163604736328</v>
       </c>
       <c r="C210" t="n">
         <v>164.0500030517578</v>
@@ -6301,11 +6313,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B211" t="n">
-        <v>161.2887268066406</v>
+        <v>161.2887115478516</v>
       </c>
       <c r="C211" t="n">
         <v>167.1300048828125</v>
@@ -6330,7 +6342,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B212" t="n">
@@ -6359,7 +6371,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B213" t="n">
@@ -6388,11 +6400,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B214" t="n">
-        <v>153.404052734375</v>
+        <v>153.4040374755859</v>
       </c>
       <c r="C214" t="n">
         <v>157.4799957275391</v>
@@ -6417,11 +6429,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B215" t="n">
-        <v>157.673583984375</v>
+        <v>157.6735687255859</v>
       </c>
       <c r="C215" t="n">
         <v>160.3999938964844</v>
@@ -6446,7 +6458,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B216" t="n">
@@ -6475,7 +6487,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B217" t="n">
@@ -6504,7 +6516,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B218" t="n">
@@ -6533,7 +6545,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B219" t="n">
@@ -6562,7 +6574,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B220" t="n">
@@ -6591,7 +6603,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B221" t="n">
@@ -6620,7 +6632,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B222" t="n">
@@ -6649,7 +6661,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B223" t="n">
@@ -6678,32 +6690,32 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B224" t="n">
-        <v>190.8399963378906</v>
+        <v>191.5</v>
       </c>
       <c r="C224" t="n">
-        <v>190.8399963378906</v>
+        <v>191.5</v>
       </c>
       <c r="D224" t="n">
-        <v>73438300</v>
+        <v>76587900</v>
       </c>
       <c r="E224" t="n">
         <v>6.949999999999999</v>
       </c>
       <c r="F224" t="n">
-        <v>27.45899227883319</v>
+        <v>27.55395683453238</v>
       </c>
       <c r="G224" t="n">
         <v>1558613439</v>
       </c>
       <c r="H224" t="n">
-        <v>297445782990.9471</v>
+        <v>298474473568.5</v>
       </c>
       <c r="I224" t="n">
-        <v>0.04711771255297126</v>
+        <v>0.04913848301547976</v>
       </c>
     </row>
   </sheetData>
@@ -6735,75 +6747,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40039</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -6839,13 +6851,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -6881,13 +6893,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -6923,13 +6935,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40039</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -6965,13 +6977,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7007,13 +7019,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7040,7 +7052,7 @@
       <c r="I7" t="n">
         <v>3.26</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K7" t="n">
@@ -7053,13 +7065,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7086,7 +7098,7 @@
       <c r="I8" t="n">
         <v>3.42</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K8" t="n">
@@ -7099,13 +7111,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40417</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7132,7 +7144,7 @@
       <c r="I9" t="n">
         <v>3.7</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K9" t="n">
@@ -7145,13 +7157,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7178,7 +7190,7 @@
       <c r="I10" t="n">
         <v>3.76</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7191,13 +7203,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7224,7 +7236,7 @@
       <c r="I11" t="n">
         <v>3.92</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K11" t="n">
@@ -7237,13 +7249,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7270,7 +7282,7 @@
       <c r="I12" t="n">
         <v>4.08</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K12" t="n">
@@ -7283,13 +7295,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7316,7 +7328,7 @@
       <c r="I13" t="n">
         <v>4.359999999999999</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K13" t="n">
@@ -7329,13 +7341,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7362,7 +7374,7 @@
       <c r="I14" t="n">
         <v>4.720000000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="K14" t="n">
@@ -7375,13 +7387,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7408,7 +7420,7 @@
       <c r="I15" t="n">
         <v>4.84</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K15" t="n">
@@ -7421,13 +7433,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7454,7 +7466,7 @@
       <c r="I16" t="n">
         <v>5.03</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="K16" t="n">
@@ -7467,13 +7479,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7500,7 +7512,7 @@
       <c r="I17" t="n">
         <v>5.04</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="K17" t="n">
@@ -7513,13 +7525,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7546,7 +7558,7 @@
       <c r="I18" t="n">
         <v>5.01</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K18" t="n">
@@ -7559,13 +7571,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7592,7 +7604,7 @@
       <c r="I19" t="n">
         <v>5.18</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K19" t="n">
@@ -7605,13 +7617,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7638,7 +7650,7 @@
       <c r="I20" t="n">
         <v>5.21</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="K20" t="n">
@@ -7651,13 +7663,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -7684,7 +7696,7 @@
       <c r="I21" t="n">
         <v>5.15</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="K21" t="n">
@@ -7697,13 +7709,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -7730,7 +7742,7 @@
       <c r="I22" t="n">
         <v>5.27</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="K22" t="n">
@@ -7743,13 +7755,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -7776,7 +7788,7 @@
       <c r="I23" t="n">
         <v>5.26</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="K23" t="n">
@@ -7789,13 +7801,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -7822,7 +7834,7 @@
       <c r="I24" t="n">
         <v>5.16</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="K24" t="n">
@@ -7835,13 +7847,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -7868,7 +7880,7 @@
       <c r="I25" t="n">
         <v>5.029999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K25" t="n">
@@ -7881,13 +7893,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -7914,7 +7926,7 @@
       <c r="I26" t="n">
         <v>4.97</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="K26" t="n">
@@ -7927,13 +7939,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -7960,7 +7972,7 @@
       <c r="I27" t="n">
         <v>4.76</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="K27" t="n">
@@ -7973,13 +7985,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8006,7 +8018,7 @@
       <c r="I28" t="n">
         <v>4.74</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="K28" t="n">
@@ -8019,13 +8031,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8052,7 +8064,7 @@
       <c r="I29" t="n">
         <v>4.779999999999999</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="K29" t="n">
@@ -8065,13 +8077,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8098,7 +8110,7 @@
       <c r="I30" t="n">
         <v>4.65</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K30" t="n">
@@ -8111,13 +8123,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42417</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8144,7 +8156,7 @@
       <c r="I31" t="n">
         <v>4.42</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42417</v>
       </c>
       <c r="K31" t="n">
@@ -8157,13 +8169,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8190,7 +8202,7 @@
       <c r="I32" t="n">
         <v>4.24</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="K32" t="n">
@@ -8203,13 +8215,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42577</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8236,7 +8248,7 @@
       <c r="I33" t="n">
         <v>4.18</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42577</v>
       </c>
       <c r="K33" t="n">
@@ -8249,13 +8261,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8282,7 +8294,7 @@
       <c r="I34" t="n">
         <v>4.18</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="K34" t="n">
@@ -8295,13 +8307,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42780</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8328,7 +8340,7 @@
       <c r="I35" t="n">
         <v>4.48</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42780</v>
       </c>
       <c r="K35" t="n">
@@ -8341,13 +8353,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8374,7 +8386,7 @@
       <c r="I36" t="n">
         <v>4.52</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="K36" t="n">
@@ -8387,13 +8399,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8420,7 +8432,7 @@
       <c r="I37" t="n">
         <v>4.51</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="K37" t="n">
@@ -8433,13 +8445,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8466,7 +8478,7 @@
       <c r="I38" t="n">
         <v>4.53</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K38" t="n">
@@ -8479,13 +8491,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43144</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8512,7 +8524,7 @@
       <c r="I39" t="n">
         <v>3.87</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43144</v>
       </c>
       <c r="K39" t="n">
@@ -8525,13 +8537,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8558,7 +8570,7 @@
       <c r="I40" t="n">
         <v>3.85</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="K40" t="n">
@@ -8571,13 +8583,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8604,7 +8616,7 @@
       <c r="I41" t="n">
         <v>4.12</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="K41" t="n">
@@ -8617,13 +8629,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -8650,7 +8662,7 @@
       <c r="I42" t="n">
         <v>4.29</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="K42" t="n">
@@ -8663,13 +8675,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -8696,7 +8708,7 @@
       <c r="I43" t="n">
         <v>5.08</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="K43" t="n">
@@ -8709,13 +8721,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -8742,7 +8754,7 @@
       <c r="I44" t="n">
         <v>4.95</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="K44" t="n">
@@ -8755,13 +8767,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -8788,7 +8800,7 @@
       <c r="I45" t="n">
         <v>5.029999999999999</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="K45" t="n">
@@ -8801,13 +8813,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -8834,7 +8846,7 @@
       <c r="I46" t="n">
         <v>4.81</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="K46" t="n">
@@ -8847,13 +8859,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -8880,7 +8892,7 @@
       <c r="I47" t="n">
         <v>4.62</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="K47" t="n">
@@ -8893,13 +8905,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -8926,7 +8938,7 @@
       <c r="I48" t="n">
         <v>4.92</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="K48" t="n">
@@ -8939,13 +8951,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -8972,7 +8984,7 @@
       <c r="I49" t="n">
         <v>4.68</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="K49" t="n">
@@ -8985,13 +8997,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9018,7 +9030,7 @@
       <c r="I50" t="n">
         <v>4.94</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="K50" t="n">
@@ -9031,13 +9043,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44236</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9064,7 +9076,7 @@
       <c r="I51" t="n">
         <v>5.17</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44236</v>
       </c>
       <c r="K51" t="n">
@@ -9077,13 +9089,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9110,7 +9122,7 @@
       <c r="I52" t="n">
         <v>5.550000000000001</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="K52" t="n">
@@ -9123,13 +9135,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9156,7 +9168,7 @@
       <c r="I53" t="n">
         <v>5.69</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="K53" t="n">
@@ -9169,13 +9181,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9202,7 +9214,7 @@
       <c r="I54" t="n">
         <v>5.76</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="K54" t="n">
@@ -9215,13 +9227,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9248,7 +9260,7 @@
       <c r="I55" t="n">
         <v>5.83</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="K55" t="n">
@@ -9261,13 +9273,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9294,7 +9306,7 @@
       <c r="I56" t="n">
         <v>5.779999999999999</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K56" t="n">
@@ -9307,13 +9319,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9340,7 +9352,7 @@
       <c r="I57" t="n">
         <v>5.819999999999999</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="K57" t="n">
@@ -9353,13 +9365,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9386,7 +9398,7 @@
       <c r="I58" t="n">
         <v>5.609999999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="K58" t="n">
@@ -9399,13 +9411,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9432,7 +9444,7 @@
       <c r="I59" t="n">
         <v>5.81</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="K59" t="n">
@@ -9445,13 +9457,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9478,7 +9490,7 @@
       <c r="I60" t="n">
         <v>5.59</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="K60" t="n">
@@ -9491,13 +9503,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9524,7 +9536,7 @@
       <c r="I61" t="n">
         <v>5.17</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K61" t="n">
@@ -9537,13 +9549,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9570,7 +9582,7 @@
       <c r="I62" t="n">
         <v>5.15</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="K62" t="n">
@@ -9583,13 +9595,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9616,7 +9628,7 @@
       <c r="I63" t="n">
         <v>5.02</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="K63" t="n">
@@ -9629,13 +9641,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -9662,7 +9674,7 @@
       <c r="I64" t="n">
         <v>5.119999999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="K64" t="n">
@@ -9675,13 +9687,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -9708,7 +9720,7 @@
       <c r="I65" t="n">
         <v>5.649999999999999</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="K65" t="n">
@@ -9721,13 +9733,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -9754,7 +9766,7 @@
       <c r="I66" t="n">
         <v>6.299999999999999</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="K66" t="n">
@@ -9767,13 +9779,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -9800,7 +9812,7 @@
       <c r="I67" t="n">
         <v>4.52</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="K67" t="n">
@@ -9813,13 +9825,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -9846,7 +9858,7 @@
       <c r="I68" t="n">
         <v>4.859999999999999</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="K68" t="n">
@@ -9859,13 +9871,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -9892,7 +9904,7 @@
       <c r="I69" t="n">
         <v>5.27</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="K69" t="n">
@@ -9905,13 +9917,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -9938,7 +9950,7 @@
       <c r="I70" t="n">
         <v>5.529999999999999</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="K70" t="n">
@@ -9951,13 +9963,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -9984,7 +9996,7 @@
       <c r="I71" t="n">
         <v>7.26</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="K71" t="n">
@@ -9997,13 +10009,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10030,7 +10042,7 @@
       <c r="I72" t="n">
         <v>7.1</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="K72" t="n">
@@ -10043,13 +10055,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10076,7 +10088,7 @@
       <c r="I73" t="n">
         <v>6.949999999999999</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="K73" t="n">
@@ -10113,52 +10125,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40039</v>
       </c>
       <c r="C2" t="n">
@@ -10187,10 +10199,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40116</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10219,10 +10231,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40207</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10251,10 +10263,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -10283,10 +10295,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40417</v>
       </c>
       <c r="C6" t="n">
@@ -10315,10 +10327,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40480</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -10347,10 +10359,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C8" t="n">
@@ -10379,10 +10391,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C9" t="n">
@@ -10411,10 +10423,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C10" t="n">
@@ -10443,10 +10455,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="C11" t="n">
@@ -10475,10 +10487,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C12" t="n">
@@ -10507,10 +10519,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="C13" t="n">
@@ -10539,10 +10551,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="C14" t="n">
@@ -10571,10 +10583,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C15" t="n">
@@ -10603,10 +10615,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C16" t="n">
@@ -10635,10 +10647,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="C17" t="n">
@@ -10667,10 +10679,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="C18" t="n">
@@ -10699,10 +10711,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41577</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="C19" t="n">
@@ -10731,10 +10743,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="C20" t="n">
@@ -10763,10 +10775,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="C21" t="n">
@@ -10795,10 +10807,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41849</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C22" t="n">
@@ -10827,10 +10839,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41941</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="C23" t="n">
@@ -10859,10 +10871,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42034</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="C24" t="n">
@@ -10891,10 +10903,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42123</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="C25" t="n">
@@ -10923,10 +10935,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42213</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="C26" t="n">
@@ -10955,10 +10967,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42303</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C27" t="n">
@@ -10987,10 +10999,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42398</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42417</v>
       </c>
       <c r="C28" t="n">
@@ -11019,10 +11031,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42482</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="C29" t="n">
@@ -11051,10 +11063,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42573</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42577</v>
       </c>
       <c r="C30" t="n">
@@ -11083,10 +11095,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42664</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="C31" t="n">
@@ -11115,10 +11127,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42780</v>
       </c>
       <c r="C32" t="n">
@@ -11147,10 +11159,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42849</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="C33" t="n">
@@ -11179,10 +11191,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42940</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="C34" t="n">
@@ -11211,10 +11223,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43031</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C35" t="n">
@@ -11243,10 +11255,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43144</v>
       </c>
       <c r="C36" t="n">
@@ -11275,10 +11287,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43213</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C37" t="n">
@@ -11307,10 +11319,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43304</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C38" t="n">
@@ -11339,10 +11351,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43395</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="C39" t="n">
@@ -11371,10 +11383,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="C40" t="n">
@@ -11403,10 +11415,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43577</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="C41" t="n">
@@ -11435,10 +11447,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43668</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="C42" t="n">
@@ -11467,10 +11479,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43759</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="C43" t="n">
@@ -11499,10 +11511,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="C44" t="n">
@@ -11531,10 +11543,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43944</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="C45" t="n">
@@ -11563,10 +11575,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44035</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="C46" t="n">
@@ -11595,10 +11607,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44126</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="C47" t="n">
@@ -11627,10 +11639,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44236</v>
       </c>
       <c r="C48" t="n">
@@ -11659,10 +11671,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44308</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="C49" t="n">
@@ -11691,10 +11703,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44399</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="C50" t="n">
@@ -11723,10 +11735,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44494</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="C51" t="n">
@@ -11755,10 +11767,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="C52" t="n">
@@ -11787,10 +11799,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44673</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C53" t="n">
@@ -11819,10 +11831,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44764</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="C54" t="n">
@@ -11851,10 +11863,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44855</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="C55" t="n">
@@ -11883,10 +11895,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="C56" t="n">
@@ -11915,10 +11927,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45037</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="C57" t="n">
@@ -11947,10 +11959,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45128</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C58" t="n">
@@ -11979,10 +11991,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45219</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="C59" t="n">
@@ -12011,10 +12023,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="C60" t="n">
@@ -12043,10 +12055,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45401</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="C61" t="n">
@@ -12075,10 +12087,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45492</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="C62" t="n">
@@ -12107,10 +12119,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45583</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="C63" t="n">
@@ -12139,10 +12151,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="C64" t="n">
@@ -12171,10 +12183,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45764</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="C65" t="n">
@@ -12203,10 +12215,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45856</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="C66" t="n">
@@ -12235,10 +12247,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45947</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="C67" t="n">
@@ -12267,10 +12279,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="C68" t="n">
@@ -12299,10 +12311,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="C69" t="n">
@@ -12331,10 +12343,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46220</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="C70" t="n">
@@ -12381,12 +12393,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/PM.xlsx
+++ b/salidas/empresas/PM.xlsx
@@ -498,7 +498,7 @@
         <v>39538</v>
       </c>
       <c r="B2" t="n">
-        <v>21.6566276550293</v>
+        <v>21.6566219329834</v>
       </c>
       <c r="C2" t="n">
         <v>50.58000183105469</v>
@@ -517,7 +517,7 @@
         <v>39568</v>
       </c>
       <c r="B3" t="n">
-        <v>21.84929275512695</v>
+        <v>21.84930610656738</v>
       </c>
       <c r="C3" t="n">
         <v>51.02999877929688</v>
@@ -536,7 +536,7 @@
         <v>39599</v>
       </c>
       <c r="B4" t="n">
-        <v>22.54720115661621</v>
+        <v>22.54720687866211</v>
       </c>
       <c r="C4" t="n">
         <v>52.65999984741211</v>
@@ -555,7 +555,7 @@
         <v>39629</v>
       </c>
       <c r="B5" t="n">
-        <v>21.33669090270996</v>
+        <v>21.33669471740723</v>
       </c>
       <c r="C5" t="n">
         <v>49.38999938964844</v>
@@ -574,7 +574,7 @@
         <v>39660</v>
       </c>
       <c r="B6" t="n">
-        <v>22.31302070617676</v>
+        <v>22.31302261352539</v>
       </c>
       <c r="C6" t="n">
         <v>51.65000152587891</v>
@@ -593,7 +593,7 @@
         <v>39691</v>
       </c>
       <c r="B7" t="n">
-        <v>23.19862365722656</v>
+        <v>23.1986198425293</v>
       </c>
       <c r="C7" t="n">
         <v>53.70000076293945</v>
@@ -612,7 +612,7 @@
         <v>39721</v>
       </c>
       <c r="B8" t="n">
-        <v>20.98689079284668</v>
+        <v>20.98689460754395</v>
       </c>
       <c r="C8" t="n">
         <v>48.09999847412109</v>
@@ -631,7 +631,7 @@
         <v>39752</v>
       </c>
       <c r="B9" t="n">
-        <v>18.96674156188965</v>
+        <v>18.96673774719238</v>
       </c>
       <c r="C9" t="n">
         <v>43.47000122070312</v>
@@ -650,7 +650,7 @@
         <v>39782</v>
       </c>
       <c r="B10" t="n">
-        <v>18.39516067504883</v>
+        <v>18.39516448974609</v>
       </c>
       <c r="C10" t="n">
         <v>42.15999984741211</v>
@@ -669,7 +669,7 @@
         <v>39813</v>
       </c>
       <c r="B11" t="n">
-        <v>19.23044395446777</v>
+        <v>19.23044586181641</v>
       </c>
       <c r="C11" t="n">
         <v>43.5099983215332</v>
@@ -688,7 +688,7 @@
         <v>39844</v>
       </c>
       <c r="B12" t="n">
-        <v>16.41947174072266</v>
+        <v>16.41946601867676</v>
       </c>
       <c r="C12" t="n">
         <v>37.15000152587891</v>
@@ -707,7 +707,7 @@
         <v>39872</v>
       </c>
       <c r="B13" t="n">
-        <v>14.79299068450928</v>
+        <v>14.79299259185791</v>
       </c>
       <c r="C13" t="n">
         <v>33.47000122070312</v>
@@ -726,7 +726,7 @@
         <v>39903</v>
       </c>
       <c r="B14" t="n">
-        <v>15.95009994506836</v>
+        <v>15.95009517669678</v>
       </c>
       <c r="C14" t="n">
         <v>35.58000183105469</v>
@@ -745,7 +745,7 @@
         <v>39933</v>
       </c>
       <c r="B15" t="n">
-        <v>16.22804069519043</v>
+        <v>16.22803115844727</v>
       </c>
       <c r="C15" t="n">
         <v>36.20000076293945</v>
@@ -764,7 +764,7 @@
         <v>39964</v>
       </c>
       <c r="B16" t="n">
-        <v>19.11501312255859</v>
+        <v>19.1150074005127</v>
       </c>
       <c r="C16" t="n">
         <v>42.63999938964844</v>
@@ -783,7 +783,7 @@
         <v>39994</v>
       </c>
       <c r="B17" t="n">
-        <v>19.80810546875</v>
+        <v>19.80810737609863</v>
       </c>
       <c r="C17" t="n">
         <v>43.61999893188477</v>
@@ -802,7 +802,7 @@
         <v>40025</v>
       </c>
       <c r="B18" t="n">
-        <v>21.16134262084961</v>
+        <v>21.16132736206055</v>
       </c>
       <c r="C18" t="n">
         <v>46.59999847412109</v>
@@ -846,7 +846,7 @@
         <v>40086</v>
       </c>
       <c r="B20" t="n">
-        <v>22.39607238769531</v>
+        <v>22.39607429504395</v>
       </c>
       <c r="C20" t="n">
         <v>48.7400016784668</v>
@@ -871,7 +871,7 @@
         <v>40117</v>
       </c>
       <c r="B21" t="n">
-        <v>21.761962890625</v>
+        <v>21.76196098327637</v>
       </c>
       <c r="C21" t="n">
         <v>47.36000061035156</v>
@@ -896,7 +896,7 @@
         <v>40147</v>
       </c>
       <c r="B22" t="n">
-        <v>22.09739685058594</v>
+        <v>22.09739875793457</v>
       </c>
       <c r="C22" t="n">
         <v>48.09000015258789</v>
@@ -921,7 +921,7 @@
         <v>40178</v>
       </c>
       <c r="B23" t="n">
-        <v>22.40534591674805</v>
+        <v>22.40535163879395</v>
       </c>
       <c r="C23" t="n">
         <v>48.18999862670898</v>
@@ -946,7 +946,7 @@
         <v>40209</v>
       </c>
       <c r="B24" t="n">
-        <v>21.15930938720703</v>
+        <v>21.15931129455566</v>
       </c>
       <c r="C24" t="n">
         <v>45.5099983215332</v>
@@ -971,7 +971,7 @@
         <v>40237</v>
       </c>
       <c r="B25" t="n">
-        <v>22.77264785766602</v>
+        <v>22.77264022827148</v>
       </c>
       <c r="C25" t="n">
         <v>48.97999954223633</v>
@@ -996,7 +996,7 @@
         <v>40268</v>
       </c>
       <c r="B26" t="n">
-        <v>24.52004051208496</v>
+        <v>24.52002716064453</v>
       </c>
       <c r="C26" t="n">
         <v>52.15999984741211</v>
@@ -1021,7 +1021,7 @@
         <v>40298</v>
       </c>
       <c r="B27" t="n">
-        <v>23.07215309143066</v>
+        <v>23.07215118408203</v>
       </c>
       <c r="C27" t="n">
         <v>49.08000183105469</v>
@@ -1046,7 +1046,7 @@
         <v>40329</v>
       </c>
       <c r="B28" t="n">
-        <v>20.74049186706543</v>
+        <v>20.74049377441406</v>
       </c>
       <c r="C28" t="n">
         <v>44.11999893188477</v>
@@ -1071,7 +1071,7 @@
         <v>40359</v>
       </c>
       <c r="B29" t="n">
-        <v>21.82248687744141</v>
+        <v>21.82247734069824</v>
       </c>
       <c r="C29" t="n">
         <v>45.84000015258789</v>
@@ -1096,7 +1096,7 @@
         <v>40390</v>
       </c>
       <c r="B30" t="n">
-        <v>24.29798889160156</v>
+        <v>24.2979793548584</v>
       </c>
       <c r="C30" t="n">
         <v>51.04000091552734</v>
@@ -1121,7 +1121,7 @@
         <v>40421</v>
       </c>
       <c r="B31" t="n">
-        <v>24.45032119750977</v>
+        <v>24.4503173828125</v>
       </c>
       <c r="C31" t="n">
         <v>51.36000061035156</v>
@@ -1171,7 +1171,7 @@
         <v>40482</v>
       </c>
       <c r="B33" t="n">
-        <v>28.17591857910156</v>
+        <v>28.17590522766113</v>
       </c>
       <c r="C33" t="n">
         <v>58.5099983215332</v>
@@ -1196,7 +1196,7 @@
         <v>40512</v>
       </c>
       <c r="B34" t="n">
-        <v>27.39579010009766</v>
+        <v>27.39578628540039</v>
       </c>
       <c r="C34" t="n">
         <v>56.88999938964844</v>
@@ -1246,7 +1246,7 @@
         <v>40574</v>
       </c>
       <c r="B36" t="n">
-        <v>27.86367988586426</v>
+        <v>27.86369132995605</v>
       </c>
       <c r="C36" t="n">
         <v>57.2400016784668</v>
@@ -1271,7 +1271,7 @@
         <v>40602</v>
       </c>
       <c r="B37" t="n">
-        <v>30.56049156188965</v>
+        <v>30.56049919128418</v>
       </c>
       <c r="C37" t="n">
         <v>62.77999877929688</v>
@@ -1300,7 +1300,7 @@
         <v>40633</v>
       </c>
       <c r="B38" t="n">
-        <v>32.27597427368164</v>
+        <v>32.27598190307617</v>
       </c>
       <c r="C38" t="n">
         <v>65.62999725341797</v>
@@ -1329,7 +1329,7 @@
         <v>40663</v>
       </c>
       <c r="B39" t="n">
-        <v>34.14969253540039</v>
+        <v>34.14968872070312</v>
       </c>
       <c r="C39" t="n">
         <v>69.44000244140625</v>
@@ -1358,7 +1358,7 @@
         <v>40694</v>
       </c>
       <c r="B40" t="n">
-        <v>35.28572463989258</v>
+        <v>35.28571701049805</v>
       </c>
       <c r="C40" t="n">
         <v>71.75</v>
@@ -1387,7 +1387,7 @@
         <v>40724</v>
       </c>
       <c r="B41" t="n">
-        <v>33.14368438720703</v>
+        <v>33.1436882019043</v>
       </c>
       <c r="C41" t="n">
         <v>66.76999664306641</v>
@@ -1416,7 +1416,7 @@
         <v>40755</v>
       </c>
       <c r="B42" t="n">
-        <v>35.32776260375977</v>
+        <v>35.32778930664062</v>
       </c>
       <c r="C42" t="n">
         <v>71.16999816894531</v>
@@ -1474,7 +1474,7 @@
         <v>40816</v>
       </c>
       <c r="B44" t="n">
-        <v>31.33598518371582</v>
+        <v>31.33599853515625</v>
       </c>
       <c r="C44" t="n">
         <v>62.38000106811523</v>
@@ -1532,7 +1532,7 @@
         <v>40877</v>
       </c>
       <c r="B46" t="n">
-        <v>38.29842376708984</v>
+        <v>38.29843902587891</v>
       </c>
       <c r="C46" t="n">
         <v>76.23999786376953</v>
@@ -1561,7 +1561,7 @@
         <v>40908</v>
       </c>
       <c r="B47" t="n">
-        <v>39.82609939575195</v>
+        <v>39.82611083984375</v>
       </c>
       <c r="C47" t="n">
         <v>78.48000335693359</v>
@@ -1590,7 +1590,7 @@
         <v>40939</v>
       </c>
       <c r="B48" t="n">
-        <v>37.94340896606445</v>
+        <v>37.94340133666992</v>
       </c>
       <c r="C48" t="n">
         <v>74.76999664306641</v>
@@ -1619,7 +1619,7 @@
         <v>40968</v>
       </c>
       <c r="B49" t="n">
-        <v>42.38376235961914</v>
+        <v>42.38374328613281</v>
       </c>
       <c r="C49" t="n">
         <v>83.51999664306641</v>
@@ -1648,7 +1648,7 @@
         <v>40999</v>
       </c>
       <c r="B50" t="n">
-        <v>45.36301422119141</v>
+        <v>45.36301803588867</v>
       </c>
       <c r="C50" t="n">
         <v>88.61000061035156</v>
@@ -1677,7 +1677,7 @@
         <v>41029</v>
       </c>
       <c r="B51" t="n">
-        <v>45.82376861572266</v>
+        <v>45.82376098632812</v>
       </c>
       <c r="C51" t="n">
         <v>89.51000213623047</v>
@@ -1706,7 +1706,7 @@
         <v>41060</v>
       </c>
       <c r="B52" t="n">
-        <v>43.26407241821289</v>
+        <v>43.26408004760742</v>
       </c>
       <c r="C52" t="n">
         <v>84.51000213623047</v>
@@ -1735,7 +1735,7 @@
         <v>41090</v>
       </c>
       <c r="B53" t="n">
-        <v>45.07544326782227</v>
+        <v>45.07542419433594</v>
       </c>
       <c r="C53" t="n">
         <v>87.26000213623047</v>
@@ -1793,7 +1793,7 @@
         <v>41152</v>
       </c>
       <c r="B55" t="n">
-        <v>46.12922286987305</v>
+        <v>46.12924194335938</v>
       </c>
       <c r="C55" t="n">
         <v>89.30000305175781</v>
@@ -1822,7 +1822,7 @@
         <v>41182</v>
       </c>
       <c r="B56" t="n">
-        <v>46.8924560546875</v>
+        <v>46.89247131347656</v>
       </c>
       <c r="C56" t="n">
         <v>89.94000244140625</v>
@@ -1851,7 +1851,7 @@
         <v>41213</v>
       </c>
       <c r="B57" t="n">
-        <v>46.1729621887207</v>
+        <v>46.17295837402344</v>
       </c>
       <c r="C57" t="n">
         <v>88.55999755859375</v>
@@ -1880,7 +1880,7 @@
         <v>41243</v>
       </c>
       <c r="B58" t="n">
-        <v>46.86116790771484</v>
+        <v>46.86117935180664</v>
       </c>
       <c r="C58" t="n">
         <v>89.87999725341797</v>
@@ -1909,7 +1909,7 @@
         <v>41274</v>
       </c>
       <c r="B59" t="n">
-        <v>43.67158889770508</v>
+        <v>43.67160797119141</v>
       </c>
       <c r="C59" t="n">
         <v>83.63999938964844</v>
@@ -1938,7 +1938,7 @@
         <v>41305</v>
       </c>
       <c r="B60" t="n">
-        <v>46.03166961669922</v>
+        <v>46.03166580200195</v>
       </c>
       <c r="C60" t="n">
         <v>88.16000366210938</v>
@@ -1967,7 +1967,7 @@
         <v>41333</v>
       </c>
       <c r="B61" t="n">
-        <v>47.90613555908203</v>
+        <v>47.90613174438477</v>
       </c>
       <c r="C61" t="n">
         <v>91.75</v>
@@ -1996,7 +1996,7 @@
         <v>41364</v>
       </c>
       <c r="B62" t="n">
-        <v>48.85886001586914</v>
+        <v>48.85884857177734</v>
       </c>
       <c r="C62" t="n">
         <v>92.70999908447266</v>
@@ -2025,7 +2025,7 @@
         <v>41394</v>
       </c>
       <c r="B63" t="n">
-        <v>50.37662506103516</v>
+        <v>50.37664413452148</v>
       </c>
       <c r="C63" t="n">
         <v>95.58999633789062</v>
@@ -2054,7 +2054,7 @@
         <v>41425</v>
       </c>
       <c r="B64" t="n">
-        <v>47.91023254394531</v>
+        <v>47.91024780273438</v>
       </c>
       <c r="C64" t="n">
         <v>90.91000366210938</v>
@@ -2083,7 +2083,7 @@
         <v>41455</v>
       </c>
       <c r="B65" t="n">
-        <v>46.10057830810547</v>
+        <v>46.10056686401367</v>
       </c>
       <c r="C65" t="n">
         <v>86.62000274658203</v>
@@ -2112,7 +2112,7 @@
         <v>41486</v>
       </c>
       <c r="B66" t="n">
-        <v>47.46303939819336</v>
+        <v>47.46304321289062</v>
       </c>
       <c r="C66" t="n">
         <v>89.18000030517578</v>
@@ -2141,7 +2141,7 @@
         <v>41517</v>
       </c>
       <c r="B67" t="n">
-        <v>44.40808868408203</v>
+        <v>44.40811920166016</v>
       </c>
       <c r="C67" t="n">
         <v>83.44000244140625</v>
@@ -2170,7 +2170,7 @@
         <v>41547</v>
       </c>
       <c r="B68" t="n">
-        <v>46.57234954833984</v>
+        <v>46.57236480712891</v>
       </c>
       <c r="C68" t="n">
         <v>86.58999633789062</v>
@@ -2199,7 +2199,7 @@
         <v>41578</v>
       </c>
       <c r="B69" t="n">
-        <v>47.93313598632812</v>
+        <v>47.93313217163086</v>
       </c>
       <c r="C69" t="n">
         <v>89.12000274658203</v>
@@ -2228,7 +2228,7 @@
         <v>41608</v>
       </c>
       <c r="B70" t="n">
-        <v>46.00763320922852</v>
+        <v>46.00761413574219</v>
       </c>
       <c r="C70" t="n">
         <v>85.54000091552734</v>
@@ -2257,7 +2257,7 @@
         <v>41639</v>
       </c>
       <c r="B71" t="n">
-        <v>47.38363265991211</v>
+        <v>47.38360595703125</v>
       </c>
       <c r="C71" t="n">
         <v>87.12999725341797</v>
@@ -2286,7 +2286,7 @@
         <v>41670</v>
       </c>
       <c r="B72" t="n">
-        <v>42.49462127685547</v>
+        <v>42.49462890625</v>
       </c>
       <c r="C72" t="n">
         <v>78.13999938964844</v>
@@ -2344,7 +2344,7 @@
         <v>41729</v>
       </c>
       <c r="B74" t="n">
-        <v>45.0496711730957</v>
+        <v>45.04966735839844</v>
       </c>
       <c r="C74" t="n">
         <v>81.87000274658203</v>
@@ -2373,7 +2373,7 @@
         <v>41759</v>
       </c>
       <c r="B75" t="n">
-        <v>47.00859069824219</v>
+        <v>47.00860977172852</v>
       </c>
       <c r="C75" t="n">
         <v>85.43000030517578</v>
@@ -2402,7 +2402,7 @@
         <v>41790</v>
       </c>
       <c r="B76" t="n">
-        <v>48.71990203857422</v>
+        <v>48.71990966796875</v>
       </c>
       <c r="C76" t="n">
         <v>88.54000091552734</v>
@@ -2431,7 +2431,7 @@
         <v>41820</v>
       </c>
       <c r="B77" t="n">
-        <v>46.87960433959961</v>
+        <v>46.87959671020508</v>
       </c>
       <c r="C77" t="n">
         <v>84.30999755859375</v>
@@ -2460,7 +2460,7 @@
         <v>41851</v>
       </c>
       <c r="B78" t="n">
-        <v>45.60071563720703</v>
+        <v>45.6007080078125</v>
       </c>
       <c r="C78" t="n">
         <v>82.01000213623047</v>
@@ -2489,7 +2489,7 @@
         <v>41882</v>
       </c>
       <c r="B79" t="n">
-        <v>47.58576965332031</v>
+        <v>47.58577346801758</v>
       </c>
       <c r="C79" t="n">
         <v>85.58000183105469</v>
@@ -2518,7 +2518,7 @@
         <v>41912</v>
       </c>
       <c r="B80" t="n">
-        <v>46.91887283325195</v>
+        <v>46.91886901855469</v>
       </c>
       <c r="C80" t="n">
         <v>83.40000152587891</v>
@@ -2547,7 +2547,7 @@
         <v>41943</v>
       </c>
       <c r="B81" t="n">
-        <v>50.07491683959961</v>
+        <v>50.07492065429688</v>
       </c>
       <c r="C81" t="n">
         <v>89.01000213623047</v>
@@ -2576,7 +2576,7 @@
         <v>41973</v>
       </c>
       <c r="B82" t="n">
-        <v>48.90476226806641</v>
+        <v>48.90475845336914</v>
       </c>
       <c r="C82" t="n">
         <v>86.93000030517578</v>
@@ -2605,7 +2605,7 @@
         <v>42004</v>
       </c>
       <c r="B83" t="n">
-        <v>46.38030242919922</v>
+        <v>46.38031005859375</v>
       </c>
       <c r="C83" t="n">
         <v>81.44999694824219</v>
@@ -2663,7 +2663,7 @@
         <v>42063</v>
       </c>
       <c r="B85" t="n">
-        <v>47.24014663696289</v>
+        <v>47.24014282226562</v>
       </c>
       <c r="C85" t="n">
         <v>82.95999908447266</v>
@@ -2692,7 +2692,7 @@
         <v>42094</v>
       </c>
       <c r="B86" t="n">
-        <v>43.43931579589844</v>
+        <v>43.4393196105957</v>
       </c>
       <c r="C86" t="n">
         <v>75.33000183105469</v>
@@ -2750,7 +2750,7 @@
         <v>42155</v>
       </c>
       <c r="B88" t="n">
-        <v>47.90260314941406</v>
+        <v>47.90261840820312</v>
       </c>
       <c r="C88" t="n">
         <v>83.06999969482422</v>
@@ -2779,7 +2779,7 @@
         <v>42185</v>
       </c>
       <c r="B89" t="n">
-        <v>46.79320526123047</v>
+        <v>46.79321670532227</v>
       </c>
       <c r="C89" t="n">
         <v>80.16999816894531</v>
@@ -2808,7 +2808,7 @@
         <v>42216</v>
       </c>
       <c r="B90" t="n">
-        <v>49.92171478271484</v>
+        <v>49.92170715332031</v>
       </c>
       <c r="C90" t="n">
         <v>85.52999877929688</v>
@@ -2837,7 +2837,7 @@
         <v>42247</v>
       </c>
       <c r="B91" t="n">
-        <v>46.57724761962891</v>
+        <v>46.57725524902344</v>
       </c>
       <c r="C91" t="n">
         <v>79.80000305175781</v>
@@ -2866,7 +2866,7 @@
         <v>42277</v>
       </c>
       <c r="B92" t="n">
-        <v>46.89640808105469</v>
+        <v>46.89640426635742</v>
       </c>
       <c r="C92" t="n">
         <v>79.33000183105469</v>
@@ -2895,7 +2895,7 @@
         <v>42308</v>
       </c>
       <c r="B93" t="n">
-        <v>52.2581787109375</v>
+        <v>52.25819396972656</v>
       </c>
       <c r="C93" t="n">
         <v>88.40000152587891</v>
@@ -2924,7 +2924,7 @@
         <v>42338</v>
       </c>
       <c r="B94" t="n">
-        <v>51.6611213684082</v>
+        <v>51.66110992431641</v>
       </c>
       <c r="C94" t="n">
         <v>87.38999938964844</v>
@@ -2953,7 +2953,7 @@
         <v>42369</v>
       </c>
       <c r="B95" t="n">
-        <v>52.58562088012695</v>
+        <v>52.58561325073242</v>
       </c>
       <c r="C95" t="n">
         <v>87.91000366210938</v>
@@ -2982,7 +2982,7 @@
         <v>42400</v>
       </c>
       <c r="B96" t="n">
-        <v>53.84177398681641</v>
+        <v>53.84177017211914</v>
       </c>
       <c r="C96" t="n">
         <v>90.01000213623047</v>
@@ -3011,7 +3011,7 @@
         <v>42429</v>
       </c>
       <c r="B97" t="n">
-        <v>54.45189666748047</v>
+        <v>54.45190811157227</v>
       </c>
       <c r="C97" t="n">
         <v>91.02999877929688</v>
@@ -3040,7 +3040,7 @@
         <v>42460</v>
       </c>
       <c r="B98" t="n">
-        <v>59.30051422119141</v>
+        <v>59.30049514770508</v>
       </c>
       <c r="C98" t="n">
         <v>98.11000061035156</v>
@@ -3069,7 +3069,7 @@
         <v>42490</v>
       </c>
       <c r="B99" t="n">
-        <v>59.30655288696289</v>
+        <v>59.30654144287109</v>
       </c>
       <c r="C99" t="n">
         <v>98.12000274658203</v>
@@ -3098,7 +3098,7 @@
         <v>42521</v>
       </c>
       <c r="B100" t="n">
-        <v>59.64503860473633</v>
+        <v>59.64503479003906</v>
       </c>
       <c r="C100" t="n">
         <v>98.68000030517578</v>
@@ -3127,7 +3127,7 @@
         <v>42551</v>
       </c>
       <c r="B101" t="n">
-        <v>62.1063232421875</v>
+        <v>62.1063346862793</v>
       </c>
       <c r="C101" t="n">
         <v>101.7200012207031</v>
@@ -3156,7 +3156,7 @@
         <v>42582</v>
       </c>
       <c r="B102" t="n">
-        <v>61.21490478515625</v>
+        <v>61.21490859985352</v>
       </c>
       <c r="C102" t="n">
         <v>100.2600021362305</v>
@@ -3185,7 +3185,7 @@
         <v>42613</v>
       </c>
       <c r="B103" t="n">
-        <v>61.013427734375</v>
+        <v>61.01342010498047</v>
       </c>
       <c r="C103" t="n">
         <v>99.93000030517578</v>
@@ -3214,7 +3214,7 @@
         <v>42643</v>
       </c>
       <c r="B104" t="n">
-        <v>59.97312545776367</v>
+        <v>59.97312164306641</v>
       </c>
       <c r="C104" t="n">
         <v>97.22000122070312</v>
@@ -3243,7 +3243,7 @@
         <v>42674</v>
       </c>
       <c r="B105" t="n">
-        <v>59.49194717407227</v>
+        <v>59.49192047119141</v>
       </c>
       <c r="C105" t="n">
         <v>96.44000244140625</v>
@@ -3272,7 +3272,7 @@
         <v>42704</v>
       </c>
       <c r="B106" t="n">
-        <v>54.45820236206055</v>
+        <v>54.45819091796875</v>
       </c>
       <c r="C106" t="n">
         <v>88.27999877929688</v>
@@ -3301,7 +3301,7 @@
         <v>42735</v>
       </c>
       <c r="B107" t="n">
-        <v>57.0875244140625</v>
+        <v>57.08750915527344</v>
       </c>
       <c r="C107" t="n">
         <v>91.48999786376953</v>
@@ -3330,7 +3330,7 @@
         <v>42766</v>
       </c>
       <c r="B108" t="n">
-        <v>59.98278045654297</v>
+        <v>59.98276519775391</v>
       </c>
       <c r="C108" t="n">
         <v>96.12999725341797</v>
@@ -3359,7 +3359,7 @@
         <v>42794</v>
       </c>
       <c r="B109" t="n">
-        <v>68.23174285888672</v>
+        <v>68.23172760009766</v>
       </c>
       <c r="C109" t="n">
         <v>109.3499984741211</v>
@@ -3388,7 +3388,7 @@
         <v>42825</v>
       </c>
       <c r="B110" t="n">
-        <v>71.09537506103516</v>
+        <v>71.09540557861328</v>
       </c>
       <c r="C110" t="n">
         <v>112.9000015258789</v>
@@ -3417,7 +3417,7 @@
         <v>42855</v>
       </c>
       <c r="B111" t="n">
-        <v>69.79817199707031</v>
+        <v>69.79815673828125</v>
       </c>
       <c r="C111" t="n">
         <v>110.8399963378906</v>
@@ -3475,7 +3475,7 @@
         <v>42916</v>
       </c>
       <c r="B113" t="n">
-        <v>74.595947265625</v>
+        <v>74.59595489501953</v>
       </c>
       <c r="C113" t="n">
         <v>117.4499969482422</v>
@@ -3504,7 +3504,7 @@
         <v>42947</v>
       </c>
       <c r="B114" t="n">
-        <v>74.12592315673828</v>
+        <v>74.12595367431641</v>
       </c>
       <c r="C114" t="n">
         <v>116.7099990844727</v>
@@ -3533,7 +3533,7 @@
         <v>42978</v>
       </c>
       <c r="B115" t="n">
-        <v>74.26566314697266</v>
+        <v>74.26567840576172</v>
       </c>
       <c r="C115" t="n">
         <v>116.9300003051758</v>
@@ -3562,7 +3562,7 @@
         <v>43008</v>
       </c>
       <c r="B116" t="n">
-        <v>71.17822265625</v>
+        <v>71.17819976806641</v>
       </c>
       <c r="C116" t="n">
         <v>111.0100021362305</v>
@@ -3591,7 +3591,7 @@
         <v>43039</v>
       </c>
       <c r="B117" t="n">
-        <v>67.09384918212891</v>
+        <v>67.09381866455078</v>
       </c>
       <c r="C117" t="n">
         <v>104.6399993896484</v>
@@ -3620,7 +3620,7 @@
         <v>43069</v>
       </c>
       <c r="B118" t="n">
-        <v>65.88198852539062</v>
+        <v>65.88200378417969</v>
       </c>
       <c r="C118" t="n">
         <v>102.75</v>
@@ -3649,7 +3649,7 @@
         <v>43100</v>
       </c>
       <c r="B119" t="n">
-        <v>68.41855621337891</v>
+        <v>68.41853332519531</v>
       </c>
       <c r="C119" t="n">
         <v>105.6500015258789</v>
@@ -3678,7 +3678,7 @@
         <v>43131</v>
       </c>
       <c r="B120" t="n">
-        <v>69.44172668457031</v>
+        <v>69.44174194335938</v>
       </c>
       <c r="C120" t="n">
         <v>107.2300033569336</v>
@@ -3707,7 +3707,7 @@
         <v>43159</v>
       </c>
       <c r="B121" t="n">
-        <v>67.05859375</v>
+        <v>67.05857849121094</v>
       </c>
       <c r="C121" t="n">
         <v>103.5500030517578</v>
@@ -3736,7 +3736,7 @@
         <v>43190</v>
       </c>
       <c r="B122" t="n">
-        <v>65.06538391113281</v>
+        <v>65.06539916992188</v>
       </c>
       <c r="C122" t="n">
         <v>99.40000152587891</v>
@@ -3765,7 +3765,7 @@
         <v>43220</v>
       </c>
       <c r="B123" t="n">
-        <v>53.67568206787109</v>
+        <v>53.6756706237793</v>
       </c>
       <c r="C123" t="n">
         <v>82</v>
@@ -3794,7 +3794,7 @@
         <v>43251</v>
       </c>
       <c r="B124" t="n">
-        <v>52.06540679931641</v>
+        <v>52.06540298461914</v>
       </c>
       <c r="C124" t="n">
         <v>79.54000091552734</v>
@@ -3852,7 +3852,7 @@
         <v>43312</v>
       </c>
       <c r="B126" t="n">
-        <v>57.28925704956055</v>
+        <v>57.28926849365234</v>
       </c>
       <c r="C126" t="n">
         <v>86.30000305175781</v>
@@ -3881,7 +3881,7 @@
         <v>43343</v>
       </c>
       <c r="B127" t="n">
-        <v>51.70638275146484</v>
+        <v>51.70639038085938</v>
       </c>
       <c r="C127" t="n">
         <v>77.88999938964844</v>
@@ -3910,7 +3910,7 @@
         <v>43373</v>
       </c>
       <c r="B128" t="n">
-        <v>54.896240234375</v>
+        <v>54.89623260498047</v>
       </c>
       <c r="C128" t="n">
         <v>81.54000091552734</v>
@@ -3939,7 +3939,7 @@
         <v>43404</v>
       </c>
       <c r="B129" t="n">
-        <v>59.29250717163086</v>
+        <v>59.29251480102539</v>
       </c>
       <c r="C129" t="n">
         <v>88.06999969482422</v>
@@ -3968,7 +3968,7 @@
         <v>43434</v>
       </c>
       <c r="B130" t="n">
-        <v>58.2557373046875</v>
+        <v>58.25571823120117</v>
       </c>
       <c r="C130" t="n">
         <v>86.52999877929688</v>
@@ -3997,7 +3997,7 @@
         <v>43465</v>
       </c>
       <c r="B131" t="n">
-        <v>45.63784027099609</v>
+        <v>45.6378288269043</v>
       </c>
       <c r="C131" t="n">
         <v>66.76000213623047</v>
@@ -4026,7 +4026,7 @@
         <v>43496</v>
       </c>
       <c r="B132" t="n">
-        <v>52.44659805297852</v>
+        <v>52.44658660888672</v>
       </c>
       <c r="C132" t="n">
         <v>76.72000122070312</v>
@@ -4055,7 +4055,7 @@
         <v>43524</v>
       </c>
       <c r="B133" t="n">
-        <v>59.43308258056641</v>
+        <v>59.43309020996094</v>
       </c>
       <c r="C133" t="n">
         <v>86.94000244140625</v>
@@ -4084,7 +4084,7 @@
         <v>43555</v>
       </c>
       <c r="B134" t="n">
-        <v>61.1894416809082</v>
+        <v>61.18945693969727</v>
       </c>
       <c r="C134" t="n">
         <v>88.38999938964844</v>
@@ -4113,7 +4113,7 @@
         <v>43585</v>
       </c>
       <c r="B135" t="n">
-        <v>59.92258834838867</v>
+        <v>59.92259979248047</v>
       </c>
       <c r="C135" t="n">
         <v>86.55999755859375</v>
@@ -4171,7 +4171,7 @@
         <v>43646</v>
       </c>
       <c r="B137" t="n">
-        <v>55.1844482421875</v>
+        <v>55.1844367980957</v>
       </c>
       <c r="C137" t="n">
         <v>78.52999877929688</v>
@@ -4200,7 +4200,7 @@
         <v>43677</v>
       </c>
       <c r="B138" t="n">
-        <v>58.75426483154297</v>
+        <v>58.75424575805664</v>
       </c>
       <c r="C138" t="n">
         <v>83.61000061035156</v>
@@ -4229,7 +4229,7 @@
         <v>43708</v>
       </c>
       <c r="B139" t="n">
-        <v>50.65893936157227</v>
+        <v>50.65892791748047</v>
       </c>
       <c r="C139" t="n">
         <v>72.08999633789062</v>
@@ -4287,7 +4287,7 @@
         <v>43769</v>
       </c>
       <c r="B141" t="n">
-        <v>58.17471694946289</v>
+        <v>58.17469024658203</v>
       </c>
       <c r="C141" t="n">
         <v>81.44000244140625</v>
@@ -4316,7 +4316,7 @@
         <v>43799</v>
       </c>
       <c r="B142" t="n">
-        <v>59.23903274536133</v>
+        <v>59.23902130126953</v>
       </c>
       <c r="C142" t="n">
         <v>82.93000030517578</v>
@@ -4345,7 +4345,7 @@
         <v>43830</v>
       </c>
       <c r="B143" t="n">
-        <v>61.62080001831055</v>
+        <v>61.62077713012695</v>
       </c>
       <c r="C143" t="n">
         <v>85.08999633789062</v>
@@ -4374,7 +4374,7 @@
         <v>43861</v>
       </c>
       <c r="B144" t="n">
-        <v>59.88999176025391</v>
+        <v>59.88997650146484</v>
       </c>
       <c r="C144" t="n">
         <v>82.69999694824219</v>
@@ -4403,7 +4403,7 @@
         <v>43890</v>
       </c>
       <c r="B145" t="n">
-        <v>59.28893280029297</v>
+        <v>59.28893661499023</v>
       </c>
       <c r="C145" t="n">
         <v>81.87000274658203</v>
@@ -4432,7 +4432,7 @@
         <v>43921</v>
       </c>
       <c r="B146" t="n">
-        <v>53.78371047973633</v>
+        <v>53.7837028503418</v>
       </c>
       <c r="C146" t="n">
         <v>72.95999908447266</v>
@@ -4490,7 +4490,7 @@
         <v>43982</v>
       </c>
       <c r="B148" t="n">
-        <v>54.07858657836914</v>
+        <v>54.07857894897461</v>
       </c>
       <c r="C148" t="n">
         <v>73.36000061035156</v>
@@ -4519,7 +4519,7 @@
         <v>44012</v>
       </c>
       <c r="B149" t="n">
-        <v>52.46882247924805</v>
+        <v>52.46881866455078</v>
       </c>
       <c r="C149" t="n">
         <v>70.05999755859375</v>
@@ -4548,7 +4548,7 @@
         <v>44043</v>
       </c>
       <c r="B150" t="n">
-        <v>57.52400207519531</v>
+        <v>57.52398681640625</v>
       </c>
       <c r="C150" t="n">
         <v>76.80999755859375</v>
@@ -4577,7 +4577,7 @@
         <v>44074</v>
       </c>
       <c r="B151" t="n">
-        <v>59.75576782226562</v>
+        <v>59.75575256347656</v>
       </c>
       <c r="C151" t="n">
         <v>79.79000091552734</v>
@@ -4606,7 +4606,7 @@
         <v>44104</v>
       </c>
       <c r="B152" t="n">
-        <v>57.04994964599609</v>
+        <v>57.04994583129883</v>
       </c>
       <c r="C152" t="n">
         <v>74.98999786376953</v>
@@ -4635,7 +4635,7 @@
         <v>44135</v>
       </c>
       <c r="B153" t="n">
-        <v>54.02969360351562</v>
+        <v>54.02968597412109</v>
       </c>
       <c r="C153" t="n">
         <v>71.01999664306641</v>
@@ -4664,7 +4664,7 @@
         <v>44165</v>
       </c>
       <c r="B154" t="n">
-        <v>57.62813949584961</v>
+        <v>57.62812805175781</v>
       </c>
       <c r="C154" t="n">
         <v>75.75</v>
@@ -4722,7 +4722,7 @@
         <v>44227</v>
       </c>
       <c r="B156" t="n">
-        <v>61.47153854370117</v>
+        <v>61.47151565551758</v>
       </c>
       <c r="C156" t="n">
         <v>79.65000152587891</v>
@@ -4751,7 +4751,7 @@
         <v>44255</v>
       </c>
       <c r="B157" t="n">
-        <v>64.84413909912109</v>
+        <v>64.84414672851562</v>
       </c>
       <c r="C157" t="n">
         <v>84.01999664306641</v>
@@ -4780,7 +4780,7 @@
         <v>44286</v>
       </c>
       <c r="B158" t="n">
-        <v>69.40659332275391</v>
+        <v>69.40660095214844</v>
       </c>
       <c r="C158" t="n">
         <v>88.73999786376953</v>
@@ -4809,7 +4809,7 @@
         <v>44316</v>
       </c>
       <c r="B159" t="n">
-        <v>74.30277252197266</v>
+        <v>74.30276489257812</v>
       </c>
       <c r="C159" t="n">
         <v>95</v>
@@ -4838,7 +4838,7 @@
         <v>44347</v>
       </c>
       <c r="B160" t="n">
-        <v>75.42124176025391</v>
+        <v>75.42120361328125</v>
       </c>
       <c r="C160" t="n">
         <v>96.43000030517578</v>
@@ -4867,7 +4867,7 @@
         <v>44377</v>
       </c>
       <c r="B161" t="n">
-        <v>78.45835876464844</v>
+        <v>78.45835113525391</v>
       </c>
       <c r="C161" t="n">
         <v>99.11000061035156</v>
@@ -4896,7 +4896,7 @@
         <v>44408</v>
       </c>
       <c r="B162" t="n">
-        <v>79.23416137695312</v>
+        <v>79.23417663574219</v>
       </c>
       <c r="C162" t="n">
         <v>100.0899963378906</v>
@@ -4983,7 +4983,7 @@
         <v>44500</v>
       </c>
       <c r="B165" t="n">
-        <v>75.76448059082031</v>
+        <v>75.76447296142578</v>
       </c>
       <c r="C165" t="n">
         <v>94.54000091552734</v>
@@ -5041,7 +5041,7 @@
         <v>44561</v>
       </c>
       <c r="B167" t="n">
-        <v>77.16992950439453</v>
+        <v>77.16991424560547</v>
       </c>
       <c r="C167" t="n">
         <v>95</v>
@@ -5070,7 +5070,7 @@
         <v>44592</v>
       </c>
       <c r="B168" t="n">
-        <v>83.54660034179688</v>
+        <v>83.54659271240234</v>
       </c>
       <c r="C168" t="n">
         <v>102.8499984741211</v>
@@ -5099,7 +5099,7 @@
         <v>44620</v>
       </c>
       <c r="B169" t="n">
-        <v>82.10067749023438</v>
+        <v>82.10065460205078</v>
       </c>
       <c r="C169" t="n">
         <v>101.0699996948242</v>
@@ -5157,7 +5157,7 @@
         <v>44681</v>
       </c>
       <c r="B171" t="n">
-        <v>82.33040618896484</v>
+        <v>82.33039855957031</v>
       </c>
       <c r="C171" t="n">
         <v>100</v>
@@ -5244,7 +5244,7 @@
         <v>44773</v>
       </c>
       <c r="B174" t="n">
-        <v>80.98760223388672</v>
+        <v>80.98759460449219</v>
       </c>
       <c r="C174" t="n">
         <v>97.15000152587891</v>
@@ -5360,7 +5360,7 @@
         <v>44895</v>
       </c>
       <c r="B178" t="n">
-        <v>84.27533721923828</v>
+        <v>84.27532958984375</v>
       </c>
       <c r="C178" t="n">
         <v>99.66999816894531</v>
@@ -5389,7 +5389,7 @@
         <v>44926</v>
       </c>
       <c r="B179" t="n">
-        <v>86.66811370849609</v>
+        <v>86.66812133789062</v>
       </c>
       <c r="C179" t="n">
         <v>101.2099990844727</v>
@@ -5418,7 +5418,7 @@
         <v>44957</v>
       </c>
       <c r="B180" t="n">
-        <v>89.26275634765625</v>
+        <v>89.26276397705078</v>
       </c>
       <c r="C180" t="n">
         <v>104.2399978637695</v>
@@ -5505,7 +5505,7 @@
         <v>45046</v>
       </c>
       <c r="B183" t="n">
-        <v>86.75762176513672</v>
+        <v>86.75759887695312</v>
       </c>
       <c r="C183" t="n">
         <v>99.97000122070312</v>
@@ -5534,7 +5534,7 @@
         <v>45077</v>
       </c>
       <c r="B184" t="n">
-        <v>78.11394500732422</v>
+        <v>78.11396026611328</v>
       </c>
       <c r="C184" t="n">
         <v>90.01000213623047</v>
@@ -5592,7 +5592,7 @@
         <v>45138</v>
       </c>
       <c r="B186" t="n">
-        <v>87.69657897949219</v>
+        <v>87.69658660888672</v>
       </c>
       <c r="C186" t="n">
         <v>99.72000122070312</v>
@@ -5621,7 +5621,7 @@
         <v>45169</v>
       </c>
       <c r="B187" t="n">
-        <v>84.47785949707031</v>
+        <v>84.47788238525391</v>
       </c>
       <c r="C187" t="n">
         <v>96.05999755859375</v>
@@ -5650,7 +5650,7 @@
         <v>45199</v>
       </c>
       <c r="B188" t="n">
-        <v>82.56270599365234</v>
+        <v>82.56269836425781</v>
       </c>
       <c r="C188" t="n">
         <v>92.58000183105469</v>
@@ -5766,7 +5766,7 @@
         <v>45322</v>
       </c>
       <c r="B192" t="n">
-        <v>82.14073944091797</v>
+        <v>82.14073181152344</v>
       </c>
       <c r="C192" t="n">
         <v>90.84999847412109</v>
@@ -5824,7 +5824,7 @@
         <v>45382</v>
       </c>
       <c r="B194" t="n">
-        <v>83.98645782470703</v>
+        <v>83.9864501953125</v>
       </c>
       <c r="C194" t="n">
         <v>91.62000274658203</v>
@@ -5882,7 +5882,7 @@
         <v>45443</v>
       </c>
       <c r="B196" t="n">
-        <v>92.93326568603516</v>
+        <v>92.93328094482422</v>
       </c>
       <c r="C196" t="n">
         <v>101.379997253418</v>
@@ -5911,7 +5911,7 @@
         <v>45473</v>
       </c>
       <c r="B197" t="n">
-        <v>94.09619140625</v>
+        <v>94.09618377685547</v>
       </c>
       <c r="C197" t="n">
         <v>101.3300018310547</v>
@@ -5940,7 +5940,7 @@
         <v>45504</v>
       </c>
       <c r="B198" t="n">
-        <v>106.9388885498047</v>
+        <v>106.9388809204102</v>
       </c>
       <c r="C198" t="n">
         <v>115.1600036621094</v>
@@ -5969,7 +5969,7 @@
         <v>45535</v>
       </c>
       <c r="B199" t="n">
-        <v>114.4884948730469</v>
+        <v>114.4885025024414</v>
       </c>
       <c r="C199" t="n">
         <v>123.2900009155273</v>
@@ -5998,7 +5998,7 @@
         <v>45565</v>
       </c>
       <c r="B200" t="n">
-        <v>113.9980773925781</v>
+        <v>113.9980850219727</v>
       </c>
       <c r="C200" t="n">
         <v>121.4000015258789</v>
@@ -6056,7 +6056,7 @@
         <v>45626</v>
       </c>
       <c r="B202" t="n">
-        <v>124.947135925293</v>
+        <v>124.9471435546875</v>
       </c>
       <c r="C202" t="n">
         <v>133.0599975585938</v>
@@ -6085,7 +6085,7 @@
         <v>45657</v>
       </c>
       <c r="B203" t="n">
-        <v>114.2671737670898</v>
+        <v>114.2671661376953</v>
       </c>
       <c r="C203" t="n">
         <v>120.3499984741211</v>
@@ -6114,7 +6114,7 @@
         <v>45688</v>
       </c>
       <c r="B204" t="n">
-        <v>123.6193313598633</v>
+        <v>123.6193237304688</v>
       </c>
       <c r="C204" t="n">
         <v>130.1999969482422</v>
@@ -6143,7 +6143,7 @@
         <v>45716</v>
       </c>
       <c r="B205" t="n">
-        <v>147.4317016601562</v>
+        <v>147.4317169189453</v>
       </c>
       <c r="C205" t="n">
         <v>155.2799987792969</v>
@@ -6201,7 +6201,7 @@
         <v>45777</v>
       </c>
       <c r="B207" t="n">
-        <v>164.1351318359375</v>
+        <v>164.1351165771484</v>
       </c>
       <c r="C207" t="n">
         <v>171.3600006103516</v>
@@ -6230,7 +6230,7 @@
         <v>45808</v>
       </c>
       <c r="B208" t="n">
-        <v>172.9759826660156</v>
+        <v>172.9759674072266</v>
       </c>
       <c r="C208" t="n">
         <v>180.5899963378906</v>
@@ -6288,7 +6288,7 @@
         <v>45869</v>
       </c>
       <c r="B210" t="n">
-        <v>158.3163604736328</v>
+        <v>158.3163757324219</v>
       </c>
       <c r="C210" t="n">
         <v>164.0500030517578</v>
@@ -6317,7 +6317,7 @@
         <v>45900</v>
       </c>
       <c r="B211" t="n">
-        <v>161.2887115478516</v>
+        <v>161.2887268066406</v>
       </c>
       <c r="C211" t="n">
         <v>167.1300048828125</v>
@@ -6404,7 +6404,7 @@
         <v>45991</v>
       </c>
       <c r="B214" t="n">
-        <v>153.4040374755859</v>
+        <v>153.404052734375</v>
       </c>
       <c r="C214" t="n">
         <v>157.4799957275391</v>
@@ -6433,7 +6433,7 @@
         <v>46022</v>
       </c>
       <c r="B215" t="n">
-        <v>157.6735687255859</v>
+        <v>157.673583984375</v>
       </c>
       <c r="C215" t="n">
         <v>160.3999938964844</v>
